--- a/research/traditional_assets/database/data/israel/israel_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_cable_tv.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.587</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,67 +612,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="V2">
-        <v>0.0004968944099378882</v>
+        <v>0.006690140845070422</v>
       </c>
       <c r="W2">
-        <v>13.65116279069768</v>
+        <v>1.546961325966851</v>
       </c>
       <c r="X2">
-        <v>0.04931670980266522</v>
+        <v>0.08373398513003794</v>
       </c>
       <c r="Y2">
-        <v>13.60184608089501</v>
-      </c>
-      <c r="Z2">
-        <v>-0</v>
-      </c>
-      <c r="AA2">
-        <v>12.62790697674419</v>
+        <v>1.463227340836813</v>
       </c>
       <c r="AB2">
-        <v>0.04994418263965327</v>
-      </c>
-      <c r="AC2">
-        <v>12.57796279410453</v>
+        <v>0.08244422488487027</v>
       </c>
       <c r="AD2">
-        <v>0.193</v>
+        <v>0.12</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.193</v>
+        <v>0.12</v>
       </c>
       <c r="AG2">
-        <v>0.189</v>
+        <v>0.101</v>
       </c>
       <c r="AH2">
-        <v>0.02341380565328157</v>
+        <v>0.04054054054054054</v>
       </c>
       <c r="AI2">
-        <v>-1.142011834319527</v>
+        <v>-0.3149606299212598</v>
       </c>
       <c r="AJ2">
-        <v>0.02293967714528462</v>
+        <v>0.03434206052363142</v>
       </c>
       <c r="AK2">
-        <v>-1.092485549132948</v>
+        <v>-0.2524999999999999</v>
       </c>
       <c r="AL2">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.002</v>
-      </c>
-      <c r="AO2">
-        <v>-271.5</v>
+        <v>-0.002</v>
       </c>
       <c r="AQ2">
-        <v>-271.5</v>
+        <v>280.5</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +680,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.587</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,67 +704,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="V3">
-        <v>0.0004968944099378882</v>
+        <v>0.006690140845070422</v>
       </c>
       <c r="W3">
-        <v>13.65116279069768</v>
+        <v>1.546961325966851</v>
       </c>
       <c r="X3">
-        <v>0.04931670980266522</v>
+        <v>0.08373398513003794</v>
       </c>
       <c r="Y3">
-        <v>13.60184608089501</v>
-      </c>
-      <c r="Z3">
-        <v>-0</v>
-      </c>
-      <c r="AA3">
-        <v>12.62790697674419</v>
+        <v>1.463227340836813</v>
       </c>
       <c r="AB3">
-        <v>0.04994418263965327</v>
-      </c>
-      <c r="AC3">
-        <v>12.57796279410453</v>
+        <v>0.08244422488487027</v>
       </c>
       <c r="AD3">
-        <v>0.193</v>
+        <v>0.12</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.193</v>
+        <v>0.12</v>
       </c>
       <c r="AG3">
-        <v>0.189</v>
+        <v>0.101</v>
       </c>
       <c r="AH3">
-        <v>0.02341380565328157</v>
+        <v>0.04054054054054054</v>
       </c>
       <c r="AI3">
-        <v>-1.142011834319527</v>
+        <v>-0.3149606299212598</v>
       </c>
       <c r="AJ3">
-        <v>0.02293967714528462</v>
+        <v>0.03434206052363142</v>
       </c>
       <c r="AK3">
-        <v>-1.092485549132948</v>
+        <v>-0.2524999999999999</v>
       </c>
       <c r="AL3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.002</v>
-      </c>
-      <c r="AO3">
-        <v>-271.5</v>
+        <v>-0.002</v>
       </c>
       <c r="AQ3">
-        <v>-271.5</v>
+        <v>280.5</v>
       </c>
     </row>
   </sheetData>
